--- a/Result/profitability/1773.xlsx
+++ b/Result/profitability/1773.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.87</v>
       </c>
       <c r="M2" t="n">
-        <v>1.72125</v>
+        <v>1.7775</v>
       </c>
       <c r="N2" t="n">
-        <v>31.88375</v>
+        <v>32.475</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.95</v>
       </c>
       <c r="M3" t="n">
-        <v>1.60125</v>
+        <v>1.665</v>
       </c>
       <c r="N3" t="n">
-        <v>29.75875</v>
+        <v>30.35</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.02</v>
       </c>
       <c r="M4" t="n">
-        <v>1.4975</v>
+        <v>1.555</v>
       </c>
       <c r="N4" t="n">
-        <v>27.99125</v>
+        <v>28.39</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.47</v>
       </c>
       <c r="M5" t="n">
-        <v>1.20125</v>
+        <v>1.2975</v>
       </c>
       <c r="N5" t="n">
-        <v>23.4225</v>
+        <v>23.83125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.51</v>
       </c>
       <c r="M6" t="n">
-        <v>1.06625</v>
+        <v>1.1325</v>
       </c>
       <c r="N6" t="n">
-        <v>21.645</v>
+        <v>21.7075</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0.96375</v>
+        <v>1.03375</v>
       </c>
       <c r="N7" t="n">
-        <v>19.755</v>
+        <v>19.9225</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.95</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8575</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>17.93875</v>
+        <v>17.82875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>1.04</v>
       </c>
       <c r="M9" t="n">
-        <v>0.735</v>
+        <v>0.7350000000000001</v>
       </c>
       <c r="N9" t="n">
         <v>15.66875</v>
@@ -1645,7 +1645,7 @@
         <v>1.1</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7637499999999999</v>
+        <v>0.76375</v>
       </c>
       <c r="N10" t="n">
         <v>16.30875</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1773</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3608</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2285</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1323</v>
+      </c>
+      <c r="F75" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="G75" t="n">
+        <v>849</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>23.54%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>29</v>
+      </c>
+      <c r="J75" t="n">
+        <v>879</v>
+      </c>
+      <c r="K75" t="n">
+        <v>709</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.9075</v>
+      </c>
+      <c r="N75" t="n">
+        <v>34.56</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.3399999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1683168316831682</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.8799999999999955</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.02343541944074556</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.7699999999999998</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.4842767295597483</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.270000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.09790419161676667</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
